--- a/outputs/gfp_results.xlsx
+++ b/outputs/gfp_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,22 +449,32 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Real Lambda Max</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>Random E[x_nodes]</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Random E[x_neighbors]</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Random Delta_GFP</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Random GFP Holds</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Random Lambda Max</t>
         </is>
       </c>
     </row>
@@ -480,29 +490,31 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.1390374331550802</v>
+        <v>13.58823529411765</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2354312354312354</v>
+        <v>23.07051282051282</v>
       </c>
       <c r="E2" t="n">
-        <v>0.09639380227615524</v>
+        <v>9.482277526395174</v>
       </c>
       <c r="F2" t="b">
         <v>1</v>
       </c>
-      <c r="G2" t="n">
-        <v>0.1443850267379679</v>
-      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1623643845866068</v>
+        <v>4.764705882352941</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01797935784863894</v>
-      </c>
-      <c r="J2" t="b">
-        <v>1</v>
-      </c>
+        <v>5.358024691358025</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.5933188090050834</v>
+      </c>
+      <c r="K2" t="b">
+        <v>1</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -516,29 +528,31 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.1464113811111044</v>
+        <v>0.1373669961003997</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2146180958361905</v>
+        <v>0.2124565257889215</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06820671472508613</v>
+        <v>0.07508952968852178</v>
       </c>
       <c r="F3" t="b">
         <v>1</v>
       </c>
-      <c r="G3" t="n">
-        <v>0.1542749757874179</v>
-      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1786743987964899</v>
+        <v>0.1542746805480808</v>
       </c>
       <c r="I3" t="n">
-        <v>0.024399423009072</v>
-      </c>
-      <c r="J3" t="b">
-        <v>1</v>
-      </c>
+        <v>0.1786742081675987</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.02439952761951791</v>
+      </c>
+      <c r="K3" t="b">
+        <v>1</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -552,29 +566,31 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>320.8235294117647</v>
+        <v>0.1449287718744321</v>
       </c>
       <c r="D4" t="n">
-        <v>461.3589743589744</v>
+        <v>0.2084142321783268</v>
       </c>
       <c r="E4" t="n">
-        <v>140.5354449472097</v>
+        <v>0.06348546030389465</v>
       </c>
       <c r="F4" t="b">
         <v>1</v>
       </c>
-      <c r="G4" t="n">
-        <v>25.52941176470588</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>28.96296296296296</v>
+        <v>0.1591490449489323</v>
       </c>
       <c r="I4" t="n">
-        <v>3.433551198257078</v>
-      </c>
-      <c r="J4" t="b">
-        <v>1</v>
-      </c>
+        <v>0.1805536272018353</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.02140458225290301</v>
+      </c>
+      <c r="K4" t="b">
+        <v>1</v>
+      </c>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -588,29 +604,31 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4.654227166783325</v>
+        <v>4.654227166783373</v>
       </c>
       <c r="D5" t="n">
-        <v>6.685241291183417</v>
+        <v>6.68524129118349</v>
       </c>
       <c r="E5" t="n">
-        <v>2.031014124400092</v>
+        <v>2.031014124400117</v>
       </c>
       <c r="F5" t="b">
         <v>1</v>
       </c>
-      <c r="G5" t="n">
-        <v>5.666274920612861</v>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>6.357971940398388</v>
+        <v>5.666274920612875</v>
       </c>
       <c r="I5" t="n">
-        <v>0.6916970197855266</v>
-      </c>
-      <c r="J5" t="b">
-        <v>1</v>
-      </c>
+        <v>6.357971940398405</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.6916970197855292</v>
+      </c>
+      <c r="K5" t="b">
+        <v>1</v>
+      </c>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -635,18 +653,20 @@
       <c r="F6" t="b">
         <v>1</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="n">
         <v>1.0489468482502</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>1.055055235781527</v>
       </c>
-      <c r="I6" t="n">
-        <v>0.006108387531327697</v>
-      </c>
-      <c r="J6" t="b">
-        <v>1</v>
-      </c>
+      <c r="J6" t="n">
+        <v>0.006108387531327475</v>
+      </c>
+      <c r="K6" t="b">
+        <v>1</v>
+      </c>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -660,34 +680,40 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.1378138527136093</v>
+        <v>0.1378138527136094</v>
       </c>
       <c r="D7" t="n">
         <v>0.212058317065143</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07424446435153365</v>
+        <v>0.07424446435153356</v>
       </c>
       <c r="F7" t="b">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.1596073058740018</v>
+        <v>21.30378417239862</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1800199405139733</v>
+        <v>0.1596073058740018</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.02041263463997156</v>
-      </c>
-      <c r="J7" t="b">
-        <v>0</v>
+        <v>0.1800199405139734</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.02041263463997159</v>
+      </c>
+      <c r="K7" t="b">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
+        <v>4.374077739178678</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Dolphins</t>
+          <t>Florentine Families</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -696,34 +722,36 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.1904761904761905</v>
+        <v>2.666666666666667</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2392857142857143</v>
+        <v>3.35</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04880952380952375</v>
+        <v>0.6833333333333336</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.1809523809523809</v>
-      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
-        <v>0.2330827067669173</v>
+        <v>2.533333333333333</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05213032581453633</v>
-      </c>
-      <c r="J8" t="b">
-        <v>1</v>
-      </c>
+        <v>3.263157894736842</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.7298245614035088</v>
+      </c>
+      <c r="K8" t="b">
+        <v>1</v>
+      </c>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Dolphins</t>
+          <t>Florentine Families</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -732,34 +760,36 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.2335080038238004</v>
+        <v>0.2335077731366817</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2851222851724456</v>
+        <v>0.2851220755115881</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05161428134864526</v>
+        <v>0.05161430237490641</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.2280407139072244</v>
-      </c>
+      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
-        <v>0.2886922781124578</v>
+        <v>0.2280403001931034</v>
       </c>
       <c r="I9" t="n">
-        <v>0.06065156420523349</v>
-      </c>
-      <c r="J9" t="b">
-        <v>1</v>
-      </c>
+        <v>0.2886919721342058</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.06065167194110235</v>
+      </c>
+      <c r="K9" t="b">
+        <v>1</v>
+      </c>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Dolphins</t>
+          <t>Florentine Families</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -768,34 +798,36 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>8.933333333333334</v>
+        <v>0.2390951849822445</v>
       </c>
       <c r="D10" t="n">
-        <v>10.5</v>
+        <v>0.2810260569753993</v>
       </c>
       <c r="E10" t="n">
-        <v>1.566666666666666</v>
+        <v>0.04193087199315484</v>
       </c>
       <c r="F10" t="b">
         <v>1</v>
       </c>
-      <c r="G10" t="n">
-        <v>8.266666666666667</v>
-      </c>
+      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>10.21052631578947</v>
+        <v>0.2338166423123517</v>
       </c>
       <c r="I10" t="n">
-        <v>1.943859649122807</v>
-      </c>
-      <c r="J10" t="b">
-        <v>1</v>
-      </c>
+        <v>0.2887972958951373</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.05498065358278559</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Dolphins</t>
+          <t>Florentine Families</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -804,34 +836,36 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>5.65366802770735</v>
+        <v>5.653668027707417</v>
       </c>
       <c r="D11" t="n">
-        <v>6.68507024779842</v>
+        <v>6.685070247798501</v>
       </c>
       <c r="E11" t="n">
-        <v>1.03140222009107</v>
+        <v>1.031402220091084</v>
       </c>
       <c r="F11" t="b">
         <v>1</v>
       </c>
-      <c r="G11" t="n">
-        <v>5.45427516425302</v>
-      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>6.634087873207494</v>
+        <v>5.454275164252988</v>
       </c>
       <c r="I11" t="n">
-        <v>1.179812708954474</v>
-      </c>
-      <c r="J11" t="b">
-        <v>1</v>
-      </c>
+        <v>6.634087873207453</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1.179812708954465</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Dolphins</t>
+          <t>Florentine Families</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -846,28 +880,30 @@
         <v>1.034030863412694</v>
       </c>
       <c r="E12" t="n">
-        <v>0.006912824385879368</v>
+        <v>0.006912824385879146</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
-      <c r="G12" t="n">
-        <v>1.025751012722078</v>
-      </c>
+      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
+        <v>1.025751012722077</v>
+      </c>
+      <c r="I12" t="n">
         <v>1.033147631597509</v>
       </c>
-      <c r="I12" t="n">
-        <v>0.00739661887543086</v>
-      </c>
-      <c r="J12" t="b">
-        <v>1</v>
-      </c>
+      <c r="J12" t="n">
+        <v>0.007396618875431082</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Dolphins</t>
+          <t>Florentine Families</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -882,22 +918,28 @@
         <v>0.2783416039787137</v>
       </c>
       <c r="E13" t="n">
-        <v>0.03626002895094266</v>
+        <v>0.03626002895094257</v>
       </c>
       <c r="F13" t="b">
         <v>1</v>
       </c>
       <c r="G13" t="n">
+        <v>2.066091573435194</v>
+      </c>
+      <c r="H13" t="n">
         <v>0.2409485677272771</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>0.2860322845123603</v>
       </c>
-      <c r="I13" t="n">
-        <v>0.04508371678508322</v>
-      </c>
-      <c r="J13" t="b">
-        <v>1</v>
+      <c r="J13" t="n">
+        <v>0.04508371678508324</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2.007343548872303</v>
       </c>
     </row>
     <row r="14">
@@ -912,29 +954,31 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.08680792891319207</v>
+        <v>21.2987012987013</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1586199751346871</v>
+        <v>44.08858267716536</v>
       </c>
       <c r="E14" t="n">
-        <v>0.07181204622149502</v>
+        <v>22.78988137846406</v>
       </c>
       <c r="F14" t="b">
         <v>1</v>
       </c>
-      <c r="G14" t="n">
-        <v>0.08441558441558442</v>
-      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.09338376305135308</v>
+        <v>6.415584415584416</v>
       </c>
       <c r="I14" t="n">
-        <v>0.008968178635768667</v>
-      </c>
-      <c r="J14" t="b">
-        <v>1</v>
-      </c>
+        <v>7.097165991902834</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.6815815763184183</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -948,29 +992,31 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.07802991544392941</v>
+        <v>0.05836660188916599</v>
       </c>
       <c r="D15" t="n">
-        <v>0.14199595151648</v>
+        <v>0.1294584648374503</v>
       </c>
       <c r="E15" t="n">
-        <v>0.06396603607255062</v>
+        <v>0.07109186294828435</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
       </c>
-      <c r="G15" t="n">
-        <v>0.1052604748234471</v>
-      </c>
+      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1181107660462638</v>
+        <v>0.105260218070115</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01285029122281671</v>
-      </c>
-      <c r="J15" t="b">
-        <v>1</v>
-      </c>
+        <v>0.1181105809136033</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.01285036284348824</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -984,29 +1030,31 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1220.883116883117</v>
+        <v>0.06374621709923489</v>
       </c>
       <c r="D16" t="n">
-        <v>2552.55905511811</v>
+        <v>0.1332772821870014</v>
       </c>
       <c r="E16" t="n">
-        <v>1331.675938234994</v>
+        <v>0.06953106508776646</v>
       </c>
       <c r="F16" t="b">
         <v>1</v>
       </c>
-      <c r="G16" t="n">
-        <v>45.53246753246754</v>
-      </c>
+      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>50.19838056680162</v>
+        <v>0.1079617297246929</v>
       </c>
       <c r="I16" t="n">
-        <v>4.665913034334082</v>
-      </c>
-      <c r="J16" t="b">
-        <v>1</v>
-      </c>
+        <v>0.119025044963923</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0110633152392301</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1020,29 +1068,31 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.566355763508412</v>
+        <v>2.566355763508378</v>
       </c>
       <c r="D17" t="n">
-        <v>4.404162726861159</v>
+        <v>4.404162726861084</v>
       </c>
       <c r="E17" t="n">
-        <v>1.837806963352747</v>
+        <v>1.837806963352706</v>
       </c>
       <c r="F17" t="b">
         <v>1</v>
       </c>
-      <c r="G17" t="n">
-        <v>5.898023541971474</v>
-      </c>
+      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
-        <v>6.465862764035661</v>
+        <v>5.898023541971392</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5678392220641868</v>
-      </c>
-      <c r="J17" t="b">
-        <v>1</v>
-      </c>
+        <v>6.465862764035568</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.5678392220641761</v>
+      </c>
+      <c r="K17" t="b">
+        <v>1</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1067,18 +1117,20 @@
       <c r="F18" t="b">
         <v>1</v>
       </c>
-      <c r="G18" t="n">
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
         <v>1.066487119319</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>1.073542679820059</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>0.007055560501059599</v>
       </c>
-      <c r="J18" t="b">
-        <v>1</v>
-      </c>
+      <c r="K18" t="b">
+        <v>1</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1104,16 +1156,22 @@
         <v>1</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1075586634639737</v>
+        <v>64.75313163688509</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1186954895264098</v>
+        <v>0.1075586634639737</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.01113682606243604</v>
-      </c>
-      <c r="J19" t="b">
-        <v>0</v>
+        <v>0.1186954895264098</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.01113682606243607</v>
+      </c>
+      <c r="K19" t="b">
+        <v>1</v>
+      </c>
+      <c r="L19" t="n">
+        <v>6.07986607755553</v>
       </c>
     </row>
     <row r="20">
@@ -1128,29 +1186,31 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.001439999912694208</v>
+        <v>3.89807976366322</v>
       </c>
       <c r="D20" t="n">
-        <v>0.004030013271698303</v>
+        <v>10.9092459264873</v>
       </c>
       <c r="E20" t="n">
-        <v>0.002590013359004095</v>
+        <v>7.011166162824084</v>
       </c>
       <c r="F20" t="b">
         <v>1</v>
       </c>
-      <c r="G20" t="n">
-        <v>0.001423357246026086</v>
-      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>0.001791336172648609</v>
+        <v>3.853028064992615</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0003679789266225232</v>
-      </c>
-      <c r="J20" t="b">
-        <v>1</v>
-      </c>
+        <v>4.849147019359785</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.9961189543671707</v>
+      </c>
+      <c r="K20" t="b">
+        <v>1</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1164,29 +1224,31 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.004786545609802777</v>
+        <v>0.004783355527093493</v>
       </c>
       <c r="D21" t="n">
-        <v>0.01766891639358925</v>
+        <v>0.01765918405287756</v>
       </c>
       <c r="E21" t="n">
-        <v>0.01288237078378647</v>
+        <v>0.01287582852578407</v>
       </c>
       <c r="F21" t="b">
         <v>1</v>
       </c>
-      <c r="G21" t="n">
-        <v>0.01528579759885097</v>
-      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
-        <v>0.02017755197969988</v>
+        <v>0.01528334833284051</v>
       </c>
       <c r="I21" t="n">
-        <v>0.004891754380848906</v>
-      </c>
-      <c r="J21" t="b">
-        <v>1</v>
-      </c>
+        <v>0.02017470047732365</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.004891352144483135</v>
+      </c>
+      <c r="K21" t="b">
+        <v>1</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1200,29 +1262,31 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>42.52511078286558</v>
+        <v>0.01157576948302947</v>
       </c>
       <c r="D22" t="n">
-        <v>83.57843880257673</v>
+        <v>0.02275090466595414</v>
       </c>
       <c r="E22" t="n">
-        <v>41.05332801971115</v>
+        <v>0.01117513518292468</v>
       </c>
       <c r="F22" t="b">
         <v>1</v>
       </c>
-      <c r="G22" t="n">
-        <v>18.68389955686854</v>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
-        <v>23.48686984857198</v>
+        <v>0.01688406963474336</v>
       </c>
       <c r="I22" t="n">
-        <v>4.802970291703438</v>
-      </c>
-      <c r="J22" t="b">
-        <v>1</v>
-      </c>
+        <v>0.02122436725901062</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.004340297624267252</v>
+      </c>
+      <c r="K22" t="b">
+        <v>1</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1236,29 +1300,31 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1.718340807888997</v>
+        <v>1.718340807888999</v>
       </c>
       <c r="D23" t="n">
-        <v>3.11996401279726</v>
+        <v>3.119964012797266</v>
       </c>
       <c r="E23" t="n">
-        <v>1.401623204908264</v>
+        <v>1.401623204908267</v>
       </c>
       <c r="F23" t="b">
         <v>1</v>
       </c>
-      <c r="G23" t="n">
-        <v>4.854869516020873</v>
-      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>5.986587583942739</v>
+        <v>4.854869516020734</v>
       </c>
       <c r="I23" t="n">
-        <v>1.131718067921866</v>
-      </c>
-      <c r="J23" t="b">
-        <v>1</v>
-      </c>
+        <v>5.986587583942557</v>
+      </c>
+      <c r="J23" t="n">
+        <v>1.131718067921823</v>
+      </c>
+      <c r="K23" t="b">
+        <v>1</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1278,23 +1344,25 @@
         <v>1.113489784503499</v>
       </c>
       <c r="E24" t="n">
-        <v>0.07232631431262915</v>
+        <v>0.07232631431262893</v>
       </c>
       <c r="F24" t="b">
         <v>1</v>
       </c>
-      <c r="G24" t="n">
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
         <v>1.039479748536184</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>1.049685620623495</v>
       </c>
-      <c r="I24" t="n">
-        <v>0.01020587208731083</v>
-      </c>
-      <c r="J24" t="b">
-        <v>1</v>
-      </c>
+      <c r="J24" t="n">
+        <v>0.01020587208731061</v>
+      </c>
+      <c r="K24" t="b">
+        <v>1</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1308,28 +1376,34 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.007535044617920303</v>
+        <v>0.00753504461792031</v>
       </c>
       <c r="D25" t="n">
-        <v>0.01938310740438164</v>
+        <v>0.01938310740438165</v>
       </c>
       <c r="E25" t="n">
-        <v>0.01184806278646133</v>
+        <v>0.01184806278646134</v>
       </c>
       <c r="F25" t="b">
         <v>1</v>
       </c>
       <c r="G25" t="n">
+        <v>9.027398981850338</v>
+      </c>
+      <c r="H25" t="n">
         <v>0.01663796625996802</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>0.02087608933722871</v>
       </c>
-      <c r="I25" t="n">
-        <v>0.004238123077260691</v>
-      </c>
-      <c r="J25" t="b">
-        <v>1</v>
+      <c r="J25" t="n">
+        <v>0.004238123077260687</v>
+      </c>
+      <c r="K25" t="b">
+        <v>1</v>
+      </c>
+      <c r="L25" t="n">
+        <v>3.83449460389697</v>
       </c>
     </row>
     <row r="26">
@@ -1344,29 +1418,31 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.0008227297529768376</v>
+        <v>2.736399158400962</v>
       </c>
       <c r="D26" t="n">
-        <v>0.002078606325832473</v>
+        <v>6.913444639718805</v>
       </c>
       <c r="E26" t="n">
-        <v>0.001255876572855635</v>
+        <v>4.177045481317844</v>
       </c>
       <c r="F26" t="b">
         <v>1</v>
       </c>
-      <c r="G26" t="n">
-        <v>0.0008003179582999643</v>
-      </c>
+      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>0.001088030523520308</v>
+        <v>2.661857529305681</v>
       </c>
       <c r="I26" t="n">
-        <v>0.000287712565220344</v>
-      </c>
-      <c r="J26" t="b">
-        <v>1</v>
-      </c>
+        <v>3.618789521228546</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.9569319919228647</v>
+      </c>
+      <c r="K26" t="b">
+        <v>1</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1380,29 +1456,31 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.00338543074887087</v>
+        <v>0.003385306832114349</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01700454165770746</v>
+        <v>0.0170035503826562</v>
       </c>
       <c r="E27" t="n">
-        <v>0.01361911090883659</v>
+        <v>0.01361824355054185</v>
       </c>
       <c r="F27" t="b">
         <v>1</v>
       </c>
-      <c r="G27" t="n">
-        <v>0.009325822763059849</v>
-      </c>
+      <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>0.01401246965985727</v>
+        <v>0.009303702173013316</v>
       </c>
       <c r="I27" t="n">
-        <v>0.004686646896797417</v>
-      </c>
-      <c r="J27" t="b">
-        <v>1</v>
-      </c>
+        <v>0.01398045987378242</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.004676757700769103</v>
+      </c>
+      <c r="K27" t="b">
+        <v>1</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1416,29 +1494,31 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>18.91794409377818</v>
+        <v>0.007659267462040562</v>
       </c>
       <c r="D28" t="n">
-        <v>54.39257469244289</v>
+        <v>0.02202180508903472</v>
       </c>
       <c r="E28" t="n">
-        <v>35.4746305986647</v>
+        <v>0.01436253762699416</v>
       </c>
       <c r="F28" t="b">
         <v>1</v>
       </c>
-      <c r="G28" t="n">
-        <v>9.632702134054703</v>
-      </c>
+      <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>13.06255645889792</v>
+        <v>0.01453834202325241</v>
       </c>
       <c r="I28" t="n">
-        <v>3.42985432484322</v>
-      </c>
-      <c r="J28" t="b">
-        <v>1</v>
-      </c>
+        <v>0.01971491600743236</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.005176573984179944</v>
+      </c>
+      <c r="K28" t="b">
+        <v>1</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1452,29 +1532,31 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.420415714569203</v>
+        <v>1.420415714569211</v>
       </c>
       <c r="D29" t="n">
-        <v>2.484285989894306</v>
+        <v>2.484285989894343</v>
       </c>
       <c r="E29" t="n">
-        <v>1.063870275325103</v>
+        <v>1.063870275325132</v>
       </c>
       <c r="F29" t="b">
         <v>1</v>
       </c>
-      <c r="G29" t="n">
-        <v>3.866654502141175</v>
-      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="n">
-        <v>5.067830556798026</v>
+        <v>3.866654502141509</v>
       </c>
       <c r="I29" t="n">
-        <v>1.201176054656851</v>
-      </c>
-      <c r="J29" t="b">
-        <v>1</v>
-      </c>
+        <v>5.067830556798512</v>
+      </c>
+      <c r="J29" t="n">
+        <v>1.201176054657003</v>
+      </c>
+      <c r="K29" t="b">
+        <v>1</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1494,23 +1576,25 @@
         <v>1.071968967016732</v>
       </c>
       <c r="E30" t="n">
-        <v>0.04363349009205542</v>
+        <v>0.04363349009205519</v>
       </c>
       <c r="F30" t="b">
         <v>1</v>
       </c>
-      <c r="G30" t="n">
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
         <v>1.027106060908259</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>1.036849363524297</v>
       </c>
-      <c r="I30" t="n">
-        <v>0.009743302616038507</v>
-      </c>
-      <c r="J30" t="b">
-        <v>1</v>
-      </c>
+      <c r="J30" t="n">
+        <v>0.009743302616038729</v>
+      </c>
+      <c r="K30" t="b">
+        <v>1</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1524,7 +1608,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.003599435006210502</v>
+        <v>0.003599435006210503</v>
       </c>
       <c r="D31" t="n">
         <v>0.01642317875702125</v>
@@ -1536,16 +1620,22 @@
         <v>1</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.01401866882678935</v>
+        <v>11.48539630565379</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.01889075395267065</v>
+        <v>0.01401866882678935</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.004872085125881304</v>
-      </c>
-      <c r="J31" t="b">
-        <v>0</v>
+        <v>0.01889075395267065</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.004872085125881302</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="n">
+        <v>2.58696651333149</v>
       </c>
     </row>
   </sheetData>
